--- a/public/attachments/Disbursment Voucher.xlsx
+++ b/public/attachments/Disbursment Voucher.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/Documents/Capstone Projects/Payroll System/public/attachments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9F646F-9D2A-F84E-A01D-B3DEC523D8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FACF2CE-E6F9-224C-8338-E53A4A73BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" xr2:uid="{191148A3-F081-644E-8FFC-E0C198E92D3A}"/>
   </bookViews>
@@ -16,7 +16,8 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -802,6 +803,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -809,6 +813,27 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,6 +869,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -865,27 +911,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -990,30 +1015,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1264,8 +1265,8 @@
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>635000</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>377567</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1631,198 +1632,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8 16383:16384" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="86"/>
       <c r="XFD1" s="26"/>
     </row>
     <row r="2" spans="1:8 16383:16384" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="81"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
       <c r="XFD2" s="26"/>
     </row>
     <row r="3" spans="1:8 16383:16384" s="6" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="82"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="84"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
       <c r="XFD3" s="26"/>
     </row>
     <row r="4" spans="1:8 16383:16384" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.25">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="87" t="s">
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="87"/>
-      <c r="G4" s="88"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="96"/>
       <c r="XFD4" s="26"/>
     </row>
     <row r="5" spans="1:8 16383:16384" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89" t="s">
+      <c r="C5" s="97"/>
+      <c r="D5" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89" t="s">
+      <c r="E5" s="97"/>
+      <c r="F5" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="90"/>
+      <c r="G5" s="98"/>
       <c r="XFD5" s="26"/>
     </row>
     <row r="6" spans="1:8 16383:16384" s="10" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="71" t="s">
+      <c r="C6" s="74"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="72"/>
-      <c r="G6" s="73"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="81"/>
       <c r="H6" s="12"/>
       <c r="XFC6" s="22"/>
       <c r="XFD6" s="26"/>
     </row>
     <row r="7" spans="1:8 16383:16384" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="74" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="76"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="84"/>
       <c r="H7" s="13"/>
       <c r="XFC7" s="23"/>
       <c r="XFD7" s="26"/>
     </row>
     <row r="8" spans="1:8 16383:16384" s="8" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="59" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
       <c r="H8" s="14"/>
       <c r="XFC8" s="24"/>
       <c r="XFD8" s="26"/>
     </row>
     <row r="9" spans="1:8 16383:16384" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
       <c r="H9" s="15"/>
       <c r="XFC9" s="25"/>
       <c r="XFD9" s="26"/>
     </row>
     <row r="10" spans="1:8 16383:16384" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
       <c r="H10" s="15"/>
       <c r="XFC10" s="25"/>
       <c r="XFD10" s="26"/>
     </row>
     <row r="11" spans="1:8 16383:16384" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
       <c r="H11" s="15"/>
       <c r="XFC11" s="25"/>
       <c r="XFD11" s="26"/>
     </row>
     <row r="12" spans="1:8 16383:16384" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="15"/>
       <c r="XFC12" s="25"/>
       <c r="XFD12" s="26"/>
     </row>
     <row r="13" spans="1:8 16383:16384" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="60"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
       <c r="H13" s="15"/>
       <c r="XFC13" s="25"/>
       <c r="XFD13" s="26"/>
     </row>
     <row r="14" spans="1:8 16383:16384" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="60"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
       <c r="H14" s="15"/>
       <c r="XFC14" s="25"/>
       <c r="XFD14" s="26"/>
     </row>
     <row r="15" spans="1:8 16383:16384" s="4" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
@@ -1835,20 +1836,20 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="56"/>
-      <c r="G16" s="57"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="65"/>
       <c r="XFD16" s="26"/>
     </row>
     <row r="17" spans="1:7 16384:16384" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="19"/>
@@ -1856,11 +1857,11 @@
     </row>
     <row r="18" spans="1:7 16384:16384" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="19"/>
@@ -1870,84 +1871,84 @@
       <c r="A19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="30"/>
       <c r="XFD19" s="26"/>
     </row>
     <row r="20" spans="1:7 16384:16384" s="4" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="43"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
       <c r="XFD20" s="26"/>
     </row>
     <row r="21" spans="1:7 16384:16384" s="4" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="42"/>
+      <c r="C21" s="57"/>
       <c r="D21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="49"/>
-      <c r="G21" s="29"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="30"/>
       <c r="XFD21" s="26"/>
     </row>
     <row r="22" spans="1:7 16384:16384" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:7 16384:16384" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54" t="s">
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="54"/>
-      <c r="G23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="56"/>
     </row>
     <row r="24" spans="1:7 16384:16384" x14ac:dyDescent="0.2">
       <c r="A24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
       <c r="D24" s="17" t="s">
         <v>30</v>
       </c>
@@ -1959,10 +1960,10 @@
       <c r="A25" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="43"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="17" t="s">
         <v>31</v>
       </c>
@@ -1974,10 +1975,10 @@
       <c r="A26" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="42"/>
+      <c r="C26" s="57"/>
       <c r="D26" s="17" t="s">
         <v>20</v>
       </c>
@@ -1989,8 +1990,8 @@
       <c r="A27" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="27" t="s">
         <v>22</v>
       </c>
@@ -1999,52 +2000,52 @@
       <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7 16384:16384" x14ac:dyDescent="0.2">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="48"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="63"/>
     </row>
     <row r="29" spans="1:7 16384:16384" x14ac:dyDescent="0.2">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="29"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="1:7 16384:16384" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="38" t="s">
+      <c r="C30" s="43"/>
+      <c r="D30" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="31"/>
+      <c r="G30" s="39"/>
     </row>
     <row r="31" spans="1:7 16384:16384" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="33"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="41"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="49"/>
       <c r="F31" s="17" t="s">
         <v>37</v>
       </c>
@@ -2054,8 +2055,8 @@
     </row>
     <row r="32" spans="1:7 16384:16384" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
@@ -2063,8 +2064,8 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="30"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
@@ -2072,8 +2073,8 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="30"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
@@ -2081,8 +2082,8 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
@@ -2090,8 +2091,8 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
@@ -2099,8 +2100,8 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
@@ -2108,21 +2109,21 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="93" t="s">
+      <c r="A39" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="94"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="95"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="33"/>
       <c r="F39" s="2"/>
       <c r="G39" s="20"/>
     </row>
@@ -2144,22 +2145,22 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="91" t="s">
+      <c r="E41" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="91"/>
-      <c r="G41" s="92"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="37"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="96"/>
-      <c r="B42" s="96"/>
-      <c r="C42" s="96"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="97" t="s">
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F42" s="97"/>
-      <c r="G42" s="98"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="35"/>
     </row>
     <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
